--- a/34th_Backgammon-championships_4b_output.xlsx
+++ b/34th_Backgammon-championships_4b_output.xlsx
@@ -1156,10 +1156,10 @@
         <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -1281,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1382,7 +1382,7 @@
         <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -1446,7 +1446,7 @@
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
@@ -1531,7 +1531,7 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -1608,7 +1608,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
